--- a/data/sce_compartment_curation/2026_curated/mitochondrial_inner_membrane_annotations.xlsx
+++ b/data/sce_compartment_curation/2026_curated/mitochondrial_inner_membrane_annotations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B416"/>
+  <dimension ref="A1:B215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YHR162W</t>
+          <t>YPR024W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YIL042C</t>
+          <t>YKL148C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YLR393W</t>
+          <t>YJR034W</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YMR064W</t>
+          <t>YML110C</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YGR096W</t>
+          <t>YDR350C</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YER077C</t>
+          <t>YGR255C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YIL157C</t>
+          <t>YFL046W</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YER182W</t>
+          <t>YML129C</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q0080</t>
+          <t>YOR176W</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YNL009W</t>
+          <t>YCL044C</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YIL006W</t>
+          <t>YBL099W</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YER017C</t>
+          <t>YER182W</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YGR236C</t>
+          <t>YKL087C</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YBL045C</t>
+          <t>YBR185C</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YBR037C</t>
+          <t>YER141W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q0140</t>
+          <t>YDR377W</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YOR020W-A</t>
+          <t>YOR205C</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YKL187C</t>
+          <t>Q0110</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YHL038C</t>
+          <t>YBR192W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YMR097C</t>
+          <t>YDR204W</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YPR021C</t>
+          <t>YGR046W</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YNR017W</t>
+          <t>YFR011C</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YNL122C</t>
+          <t>YLR283W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YDR384C</t>
+          <t>YOL095C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YKL162C</t>
+          <t>YMR257C</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YDR185C</t>
+          <t>YGR257C</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YDR119W-A</t>
+          <t>YEL052W</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YJL104W</t>
+          <t>YLR395C</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YIL077C</t>
+          <t>YDR119W-A</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YDR237W</t>
+          <t>YOR211C</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YGR165W</t>
+          <t>YDR322C-A</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YNL169C</t>
+          <t>YLR193C</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YFL036W</t>
+          <t>YJR080C</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YLR038C</t>
+          <t>YNR045W</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YLR091W</t>
+          <t>Q0085</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YOL042W</t>
+          <t>YAL039C</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YHR100C</t>
+          <t>YML030W</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YDL217C</t>
+          <t>YKL016C</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YDR322W</t>
+          <t>YMR241W</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q0070</t>
+          <t>YOL027C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YER183C</t>
+          <t>YDR381C-A</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YDR316W</t>
+          <t>YGR096W</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YOR271C</t>
+          <t>YJL062W-A</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YCR010C</t>
+          <t>YGL119W</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YKL113C</t>
+          <t>YIL006W</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YCL009C</t>
+          <t>YMR089C</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YPR020W</t>
+          <t>YNL052W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YDL222C</t>
+          <t>YOR037W</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YLR295C</t>
+          <t>YOR065W</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YOL096C</t>
+          <t>YLR348C</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YJL102W</t>
+          <t>YKL141W</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YMR150C</t>
+          <t>YIL022W</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YJR034W</t>
+          <t>YLR203C</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q0160</t>
+          <t>YPL134C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YKL003C</t>
+          <t>YBR262C</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YML110C</t>
+          <t>YIL134W</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YOL059W</t>
+          <t>YOR125C</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YLR201C</t>
+          <t>YGR112W</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YPL098C</t>
+          <t>YMR056C</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YOR147W</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YBL013W</t>
+          <t>YLR008C</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YBR047W</t>
+          <t>YNL100W</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YMR158W</t>
+          <t>YPR125W</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YMR256C</t>
+          <t>YBL030C</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YHR168W</t>
+          <t>YMR256C</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YMR038C</t>
+          <t>YBR291C</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YLR251W</t>
+          <t>YGR174C</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YNL098C</t>
+          <t>YCL057C-A</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YPL109C</t>
+          <t>YLR393W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YBL059W</t>
+          <t>YGR132C</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YPL224C</t>
+          <t>YHR198C</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YIL155C</t>
+          <t>YER014W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YER053C</t>
+          <t>YHR168W</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YGR084C</t>
+          <t>YLR201C</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YER086W</t>
+          <t>YPL078C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YOL095C</t>
+          <t>YHR001W-A</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YBR003W</t>
+          <t>YOR334W</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YPR024W</t>
+          <t>YPL109C</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q0120</t>
+          <t>YPL132W</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YPL172C</t>
+          <t>YDL142C</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YOR354C</t>
+          <t>YBR104W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YGR147C</t>
+          <t>YJL104W</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YPR033C</t>
+          <t>YER170W</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YER014W</t>
+          <t>YKL011C</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YBR084W</t>
+          <t>YEL006W</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YBR024W</t>
+          <t>YBL095W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YMR108W</t>
+          <t>YJL003W</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YOR211C</t>
+          <t>YBR227C</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YML025C</t>
+          <t>YLR164W</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YPL005W</t>
+          <t>Q0045</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YJL133W</t>
+          <t>YPR191W</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Q0045</t>
+          <t>YDR282C</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YEL059C-A</t>
+          <t>YDR375C</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YBL022C</t>
+          <t>YJR045C</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YGR150C</t>
+          <t>YLR289W</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YOR266W</t>
+          <t>YKR065C</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YNL256W</t>
+          <t>YNL328C</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YJL161W</t>
+          <t>YGL080W</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YMR307W</t>
+          <t>YDL183C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YKR042W</t>
+          <t>YJL133W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YMR003W</t>
+          <t>YNR040W</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YPR010C-A</t>
+          <t>YMR302C</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YHL004W</t>
+          <t>YNL003C</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YHL014C</t>
+          <t>YGR062C</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Q0050</t>
+          <t>YGR183C</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YKL011C</t>
+          <t>YLR295C</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YOR330C</t>
+          <t>YBR037C</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YOR350C</t>
+          <t>YOR130C</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YML081C-A</t>
+          <t>YDR393W</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YBR104W</t>
+          <t>YDL198C</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YDR381C-A</t>
+          <t>YER053C</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YDR065W</t>
+          <t>YOL008W</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YOR356W</t>
+          <t>YMR115W</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YKL056C</t>
+          <t>YJL143W</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YKR065C</t>
+          <t>YMR098C</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YER125W</t>
+          <t>YPL270W</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YDR393W</t>
+          <t>YHR002W</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YPL118W</t>
+          <t>YEL059C-A</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YDR376W</t>
+          <t>Q0275</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YLR290C</t>
+          <t>YOR356W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YFR045W</t>
+          <t>YNR018W</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YLR059C</t>
+          <t>YOL096C</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YGL236C</t>
+          <t>YLR139C</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YOR147W</t>
+          <t>YER153C</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YDR061W</t>
+          <t>YML120C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YGR062C</t>
+          <t>YNR041C</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YJL003W</t>
+          <t>YPR061C</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YPL132W</t>
+          <t>Q0250</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YIL016W</t>
+          <t>YJR095W</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YLR084C</t>
+          <t>YPR021C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YJL063C</t>
+          <t>YDR376W</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Q0250</t>
+          <t>YBL045C</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YOR037W</t>
+          <t>YDR231C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YNL125C</t>
+          <t>YDR185C</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YPR125W</t>
+          <t>YBR024W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YGL059W</t>
+          <t>YHR194W</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YGR174C</t>
+          <t>YJR077C</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YDL036C</t>
+          <t>YIR024C</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YDL207W</t>
+          <t>YGR101W</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YOR100C</t>
+          <t>YLL041C</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YLR077W</t>
+          <t>YGR222W</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YJL208C</t>
+          <t>YLR067C</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YHR001W-A</t>
+          <t>YEL024W</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YDL067C</t>
+          <t>YMR301C</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YML030W</t>
+          <t>YIL157C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YCL057C-A</t>
+          <t>YOR222W</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YML091C</t>
+          <t>YDL067C</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YLR390W</t>
+          <t>YMR150C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YML072C</t>
+          <t>YDR298C</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YDR204W</t>
+          <t>YPL005W</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YLR164W</t>
+          <t>YHR162W</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YFR033C</t>
+          <t>YOL077W-A</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YIL105C</t>
+          <t>YDR058C</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YBR039W</t>
+          <t>YNR017W</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YMR023C</t>
+          <t>YKR042W</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YJL209W</t>
+          <t>YGL191W</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YLR139C</t>
+          <t>YHR199C</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YKL208W</t>
+          <t>YKR052C</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YGR255C</t>
+          <t>YOR266W</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YBR251W</t>
+          <t>YDL217C</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YPR134W</t>
+          <t>YGL107C</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YHR011W</t>
+          <t>YJL166W</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YHR135C</t>
+          <t>YBR039W</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YDR033W</t>
+          <t>YDR079W</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YLR348C</t>
+          <t>YPR011C</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YJL143W</t>
+          <t>YLR038C</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YJR045C</t>
+          <t>YGR243W</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YOL023W</t>
+          <t>YMR097C</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YER168C</t>
+          <t>YKL195W</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YLR203C</t>
+          <t>YGR110W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YER080W</t>
+          <t>YNL169C</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YFL016C</t>
+          <t>YIL155C</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YPL097W</t>
+          <t>YPR010C-A</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YOR022C</t>
+          <t>YBR085W</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YKR087C</t>
+          <t>YPL060W</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YLR008C</t>
+          <t>YPL099C</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YLR188W</t>
+          <t>YKL120W</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YDR231C</t>
+          <t>YDR178W</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YPR166C</t>
+          <t>YFR045W</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YPR058W</t>
+          <t>YPL063W</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YNL306W</t>
+          <t>YOR271C</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YJL147C</t>
+          <t>YBR044C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YIL087C</t>
+          <t>YDR236C</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YBR163W</t>
+          <t>YFR033C</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YLR067C</t>
+          <t>YLR077W</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YEL006W</t>
+          <t>YJR121W</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YEL052W</t>
+          <t>YLR204W</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YER069W</t>
+          <t>YJL054W</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YPL060W</t>
+          <t>YDL119C</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YDL183C</t>
+          <t>YHR100C</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YEL030W</t>
+          <t>YPL103C</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YGR193C</t>
+          <t>YJL045W</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YKL055C</t>
+          <t>YOR100C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YPL231W</t>
+          <t>YPR058W</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YNL137C</t>
+          <t>YGR231C</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YGL191W</t>
+          <t>YKR016W</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YDR462W</t>
+          <t>YDL174C</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YDL027C</t>
+          <t>YER017C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YDL119C</t>
+          <t>YDR529C</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YGR033C</t>
+          <t>YKR087C</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YMR166C</t>
+          <t>YDR316W</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YPL103C</t>
+          <t>YLR251W</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YOL008W</t>
+          <t>YGR033C</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YER153C</t>
+          <t>YBR003W</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YER141W</t>
+          <t>YMR166C</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YPL222W</t>
+          <t>YGR235C</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YMR241W</t>
+          <t>YJL208C</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YDR232W</t>
+          <t>YLR188W</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YBL030C</t>
+          <t>YIL111W</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YJR101W</t>
+          <t>YLR253W</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YBR121C</t>
+          <t>YPR140W</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YPR011C</t>
+          <t>YER154W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YKL016C</t>
+          <t>YDL027C</t>
         </is>
       </c>
     </row>
@@ -2571,2017 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YJL062W-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="n">
-        <v>214</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>YKL155C</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>YOR196C</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="1" t="n">
-        <v>216</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>YNR045W</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="n">
-        <v>217</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>YGL119W</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>YPL078C</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="1" t="n">
-        <v>219</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>YDR377W</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>YLR312W-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="1" t="n">
-        <v>221</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>YNR002C</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>222</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>YMR145C</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>223</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>YOR017W</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>224</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Q0085</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>YDR529C</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>YJR095W</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="1" t="n">
-        <v>227</v>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>YJL054W</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>YDL044C</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>YBL095W</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="1" t="n">
-        <v>230</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>YGR116W</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>YLL041C</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>YBL038W</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>YBR185C</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>YGL129C</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>YMR089C</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>YMR302C</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Q0130</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>YBR282W</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>YMR188C</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>YDL174C</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>YBL099W</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>YNL177C</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>YPL063W</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>YPR061C</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Q0275</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>246</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>YER019W</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="1" t="n">
-        <v>247</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>YFL046W</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>YOR334W</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>YJR077C</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>YDR058C</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>251</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>YKL217W</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>YGR257C</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>253</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>YDR079W</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>254</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>YBR044C</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>255</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>YLR395C</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="1" t="n">
-        <v>256</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>YKL133C</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="1" t="n">
-        <v>257</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>YNL185C</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="1" t="n">
-        <v>258</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>YJL166W</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="1" t="n">
-        <v>259</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>YNL071W</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="1" t="n">
-        <v>260</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Q0065</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="1" t="n">
-        <v>261</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>YDR322C-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="1" t="n">
-        <v>262</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>YGR132C</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="1" t="n">
-        <v>263</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>YJR080C</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="1" t="n">
-        <v>264</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>YPR191W</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="1" t="n">
-        <v>265</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>YGR235C</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="1" t="n">
-        <v>266</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>YDR347W</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="1" t="n">
-        <v>267</v>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>YJL171C</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="1" t="n">
-        <v>268</v>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>YOL077W-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="1" t="n">
-        <v>269</v>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>YKL195W</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="1" t="n">
-        <v>270</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>YBR262C</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="1" t="n">
-        <v>271</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>YHR198C</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="1" t="n">
-        <v>272</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>YPL029W</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="1" t="n">
-        <v>273</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>YDL164C</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="1" t="n">
-        <v>274</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>YPL270W</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="1" t="n">
-        <v>275</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>YCR004C</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="1" t="n">
-        <v>276</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>YGL226W</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="1" t="n">
-        <v>277</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>YFR011C</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="1" t="n">
-        <v>278</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>YMR115W</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="1" t="n">
-        <v>279</v>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>YNR018W</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="1" t="n">
-        <v>280</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>YDR405W</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="1" t="n">
-        <v>281</v>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>YJR100C</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="1" t="n">
-        <v>282</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>YOR305W</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="1" t="n">
-        <v>283</v>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>YDL198C</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="1" t="n">
-        <v>284</v>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>YML120C</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="1" t="n">
-        <v>285</v>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>YPR149W</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="1" t="n">
-        <v>286</v>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>YGR231C</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="1" t="n">
-        <v>287</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>YBR085W</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="1" t="n">
-        <v>288</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>YAL039C</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>289</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>YGR222W</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>290</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>YMR193W</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>291</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>YMR066W</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>292</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>YKL087C</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>293</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>YOR221C</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>294</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>YNL211C</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>295</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>YBR192W</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="1" t="n">
-        <v>296</v>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>YDR298C</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="1" t="n">
-        <v>297</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>YPL099C</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>YJR003C</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="1" t="n">
-        <v>299</v>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>YNL052W</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>YML128C</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="1" t="n">
-        <v>301</v>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>YER170W</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="1" t="n">
-        <v>302</v>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>YHR002W</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="1" t="n">
-        <v>303</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>YMR257C</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>YDR375C</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="1" t="n">
-        <v>305</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>YIL134W</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="1" t="n">
-        <v>306</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>YLR193C</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="1" t="n">
-        <v>307</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>YDR032C</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="1" t="n">
-        <v>308</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>YDR494W</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="1" t="n">
-        <v>309</v>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>YIL022W</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="1" t="n">
-        <v>310</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>YBR078W</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="n">
-        <v>311</v>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>YKL120W</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="1" t="n">
-        <v>312</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>YER154W</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>313</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>YLR439W</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>314</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>YNR040W</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="1" t="n">
-        <v>315</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>YBR291C</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="1" t="n">
-        <v>316</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>YMR056C</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="n">
-        <v>317</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>YDR041W</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="n">
-        <v>318</v>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>YLR204W</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="n">
-        <v>319</v>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>YDL142C</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="n">
-        <v>320</v>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>YGR220C</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="n">
-        <v>321</v>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>YGR183C</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="1" t="n">
-        <v>322</v>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Q0060</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="1" t="n">
-        <v>323</v>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>YNL005C</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="1" t="n">
-        <v>324</v>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>YHR147C</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="1" t="n">
-        <v>325</v>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>YPR116W</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="1" t="n">
-        <v>326</v>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>YML129C</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="1" t="n">
-        <v>327</v>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>YDR116C</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="1" t="n">
-        <v>328</v>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>YKL138C</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="1" t="n">
-        <v>329</v>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>YJL023C</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="1" t="n">
-        <v>330</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>YGR243W</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="1" t="n">
-        <v>331</v>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>YHR194W</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="1" t="n">
-        <v>332</v>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>YKR016W</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="1" t="n">
-        <v>333</v>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>YOR086C</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="1" t="n">
-        <v>334</v>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>YGR171C</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="1" t="n">
-        <v>335</v>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>YDR178W</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="1" t="n">
-        <v>336</v>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>YOR222W</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="1" t="n">
-        <v>337</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>YDL215C</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="1" t="n">
-        <v>338</v>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>YOR176W</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="1" t="n">
-        <v>339</v>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>YOL027C</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="1" t="n">
-        <v>340</v>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>YIL111W</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="n">
-        <v>341</v>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>YDR236C</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="1" t="n">
-        <v>342</v>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>YBR054W</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="1" t="n">
-        <v>343</v>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>YOR130C</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="1" t="n">
-        <v>344</v>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>YLR289W</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="1" t="n">
-        <v>345</v>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>YJL180C</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="n">
-        <v>346</v>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>YGL080W</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="1" t="n">
-        <v>347</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>YMR301C</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="1" t="n">
-        <v>348</v>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>YDR282C</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="1" t="n">
-        <v>349</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>YNL315C</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="1" t="n">
-        <v>350</v>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>YLR283W</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="1" t="n">
-        <v>351</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>YPL134C</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="1" t="n">
-        <v>352</v>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>YIR021W</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="1" t="n">
-        <v>353</v>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>YPR140W</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="1" t="n">
-        <v>354</v>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>YMR212C</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="1" t="n">
-        <v>355</v>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>YOR205C</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="1" t="n">
-        <v>356</v>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>YBR227C</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="1" t="n">
-        <v>357</v>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>YMR177W</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="1" t="n">
-        <v>358</v>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>YCL044C</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="1" t="n">
-        <v>359</v>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>YKL170W</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="1" t="n">
-        <v>360</v>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>YDR233C</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="1" t="n">
-        <v>361</v>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>YGL136C</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="1" t="n">
-        <v>362</v>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>YKL148C</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="1" t="n">
-        <v>363</v>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>YJR121W</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="1" t="n">
-        <v>364</v>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>YGL107C</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>365</v>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>YKL141W</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="1" t="n">
-        <v>366</v>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>YLR090W</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="1" t="n">
-        <v>367</v>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>YGL064C</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="1" t="n">
-        <v>368</v>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>YGR046W</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="1" t="n">
-        <v>369</v>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>YPL215W</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="1" t="n">
-        <v>370</v>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>YGL057C</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="1" t="n">
-        <v>371</v>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>YNR041C</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" s="1" t="n">
-        <v>372</v>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>YMR024W</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="1" t="n">
-        <v>373</v>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>YNL328C</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="1" t="n">
-        <v>374</v>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>YLR239C</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>375</v>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>YDR258C</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>376</v>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>YDR197W</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>377</v>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>YKR052C</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="1" t="n">
-        <v>378</v>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>YHR199C</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="1" t="n">
-        <v>379</v>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>YKL029C</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="1" t="n">
-        <v>380</v>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>YOR065W</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="1" t="n">
-        <v>381</v>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>YOR201C</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="1" t="n">
-        <v>382</v>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>YEL024W</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" s="1" t="n">
-        <v>383</v>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>YER058W</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="1" t="n">
-        <v>384</v>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>YCL017C</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="1" t="n">
-        <v>385</v>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>YNL100W</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="1" t="n">
-        <v>386</v>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>YCL004W</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="1" t="n">
-        <v>387</v>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>YIR024C</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="1" t="n">
-        <v>388</v>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>YER020W</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" s="1" t="n">
-        <v>389</v>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>YCR046C</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="1" t="n">
-        <v>390</v>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>YOR125C</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="1" t="n">
-        <v>391</v>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>YDL202W</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="1" t="n">
-        <v>392</v>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>YKL134C</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="1" t="n">
-        <v>393</v>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>YGR112W</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="1" t="n">
-        <v>394</v>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Q0110</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>395</v>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>YMR228W</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" s="1" t="n">
-        <v>396</v>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>YML052W</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="1" t="n">
-        <v>397</v>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>YGR110W</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="1" t="n">
-        <v>398</v>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>YDR350C</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="1" t="n">
-        <v>399</v>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>YOL053W</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="1" t="n">
-        <v>400</v>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>YLR253W</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>YMR282C</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="1" t="n">
-        <v>402</v>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>YHR120W</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="1" t="n">
-        <v>403</v>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>YGR101W</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="1" t="n">
-        <v>404</v>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>YDL085W</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="1" t="n">
-        <v>405</v>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>YLR342W</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="1" t="n">
-        <v>406</v>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Q0055</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="1" t="n">
-        <v>407</v>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>YLR382C</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="1" t="n">
-        <v>408</v>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>YJL045W</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="1" t="n">
-        <v>409</v>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>YER166W</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="1" t="n">
-        <v>410</v>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>YMR157C</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="1" t="n">
-        <v>411</v>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>YNL003C</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="1" t="n">
-        <v>412</v>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>YMR098C</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="1" t="n">
-        <v>413</v>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>YDR194C</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="1" t="n">
-        <v>414</v>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>YNL252C</t>
+          <t>YMR023C</t>
         </is>
       </c>
     </row>
